--- a/output/2025_estado_nutricional_por_SS.xlsx
+++ b/output/2025_estado_nutricional_por_SS.xlsx
@@ -310,16 +310,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -335,7 +327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -343,30 +335,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -665,276 +639,276 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:89">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" t="s">
         <v>59</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" t="s">
         <v>61</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" t="s">
         <v>62</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" t="s">
         <v>63</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" t="s">
         <v>64</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" t="s">
         <v>65</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" t="s">
         <v>66</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>67</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" t="s">
         <v>68</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" t="s">
         <v>69</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" t="s">
         <v>70</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BU1" t="s">
         <v>71</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" t="s">
         <v>72</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" t="s">
         <v>73</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" t="s">
         <v>74</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" t="s">
         <v>75</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" t="s">
         <v>76</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" t="s">
         <v>77</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" t="s">
         <v>78</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" t="s">
         <v>79</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" t="s">
         <v>80</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" t="s">
         <v>81</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" t="s">
         <v>82</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" t="s">
         <v>83</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CH1" t="s">
         <v>84</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" t="s">
         <v>85</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" t="s">
         <v>86</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:89">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -1185,7 +1159,7 @@
       </c>
     </row>
     <row r="3" spans="1:89">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -1321,31 +1295,31 @@
         <v>0.1035166545345014</v>
       </c>
       <c r="AT3">
-        <v>3662</v>
+        <v>3708</v>
       </c>
       <c r="AU3">
-        <v>926</v>
+        <v>939</v>
       </c>
       <c r="AV3">
-        <v>0.2528672856362643</v>
+        <v>0.2532362459546926</v>
       </c>
       <c r="AW3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AX3">
-        <v>0.0204806116876024</v>
+        <v>0.02049622437971953</v>
       </c>
       <c r="BA3">
-        <v>1196</v>
+        <v>1211</v>
       </c>
       <c r="BB3">
-        <v>0.326597487711633</v>
+        <v>0.3265911542610572</v>
       </c>
       <c r="BC3">
-        <v>1465</v>
+        <v>1482</v>
       </c>
       <c r="BD3">
-        <v>0.4000546149645003</v>
+        <v>0.3996763754045308</v>
       </c>
       <c r="BE3">
         <v>844</v>
@@ -1375,68 +1349,68 @@
         <v>0.4514218009478673</v>
       </c>
       <c r="BP3">
-        <v>45900</v>
+        <v>46209</v>
       </c>
       <c r="BQ3">
-        <v>16488</v>
+        <v>16594</v>
       </c>
       <c r="BR3">
-        <v>0.3592156862745098</v>
+        <v>0.359107533164535</v>
       </c>
       <c r="BS3">
-        <v>5350</v>
+        <v>5386</v>
       </c>
       <c r="BT3">
-        <v>0.116557734204793</v>
+        <v>0.1165573805968534</v>
       </c>
       <c r="BW3">
-        <v>13096</v>
+        <v>13185</v>
       </c>
       <c r="BX3">
-        <v>0.2853159041394335</v>
+        <v>0.2853340258391223</v>
       </c>
       <c r="BY3">
-        <v>10966</v>
+        <v>11044</v>
       </c>
       <c r="BZ3">
-        <v>0.2389106753812636</v>
+        <v>0.2390010603994893</v>
       </c>
       <c r="CA3">
-        <v>21030</v>
+        <v>21269</v>
       </c>
       <c r="CB3">
-        <v>9399</v>
+        <v>9508</v>
       </c>
       <c r="CC3">
-        <v>0.4469329529243937</v>
+        <v>0.4470355917062391</v>
       </c>
       <c r="CD3">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="CE3">
-        <v>0.06219686162624822</v>
+        <v>0.06159198833983733</v>
       </c>
       <c r="CF3">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="CG3">
-        <v>0.01145981930575369</v>
+        <v>0.01166016267807607</v>
       </c>
       <c r="CH3">
-        <v>4772</v>
+        <v>4825</v>
       </c>
       <c r="CI3">
-        <v>0.2269139324774132</v>
+        <v>0.2268559875875688</v>
       </c>
       <c r="CJ3">
-        <v>5310</v>
+        <v>5378</v>
       </c>
       <c r="CK3">
-        <v>0.2524964336661912</v>
+        <v>0.2528562696882787</v>
       </c>
     </row>
     <row r="4" spans="1:89">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -1687,7 +1661,7 @@
       </c>
     </row>
     <row r="5" spans="1:89">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -1938,258 +1912,258 @@
       </c>
     </row>
     <row r="6" spans="1:89">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
-        <v>31919</v>
+        <v>31108</v>
       </c>
       <c r="C6">
-        <v>19354</v>
+        <v>18833</v>
       </c>
       <c r="D6">
-        <v>0.6063473166452583</v>
+        <v>0.6054069692683554</v>
       </c>
       <c r="E6">
-        <v>1638</v>
+        <v>1603</v>
       </c>
       <c r="F6">
-        <v>0.05131739716156521</v>
+        <v>0.05153015301530153</v>
       </c>
       <c r="G6">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="H6">
-        <v>0.009586766502709985</v>
+        <v>0.009483091166259483</v>
       </c>
       <c r="I6">
-        <v>7172</v>
+        <v>6993</v>
       </c>
       <c r="J6">
-        <v>0.2246937560700523</v>
+        <v>0.2247974797479748</v>
       </c>
       <c r="K6">
-        <v>3317</v>
+        <v>3248</v>
       </c>
       <c r="L6">
-        <v>0.1039192957172844</v>
+        <v>0.1044104410441044</v>
       </c>
       <c r="M6">
-        <v>15204</v>
+        <v>14868</v>
       </c>
       <c r="N6">
-        <v>8950</v>
+        <v>8742</v>
       </c>
       <c r="O6">
-        <v>0.5886608787161274</v>
+        <v>0.5879741727199355</v>
       </c>
       <c r="P6">
-        <v>920</v>
+        <v>893</v>
       </c>
       <c r="Q6">
-        <v>0.06051039200210471</v>
+        <v>0.06006187785848803</v>
       </c>
       <c r="R6">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="S6">
-        <v>0.01072086293080768</v>
+        <v>0.01076136669357008</v>
       </c>
       <c r="T6">
-        <v>2927</v>
+        <v>2872</v>
       </c>
       <c r="U6">
-        <v>0.1925151275980005</v>
+        <v>0.193166532149583</v>
       </c>
       <c r="V6">
-        <v>2229</v>
+        <v>2186</v>
       </c>
       <c r="W6">
-        <v>0.1466061562746646</v>
+        <v>0.1470271724509013</v>
       </c>
       <c r="X6">
-        <v>33413</v>
+        <v>32803</v>
       </c>
       <c r="Y6">
-        <v>16486</v>
+        <v>16140</v>
       </c>
       <c r="Z6">
-        <v>0.4934007721545506</v>
+        <v>0.4920281681553517</v>
       </c>
       <c r="AA6">
-        <v>1732</v>
+        <v>1697</v>
       </c>
       <c r="AB6">
-        <v>0.0518361116930536</v>
+        <v>0.05173307319452489</v>
       </c>
       <c r="AC6">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="AD6">
-        <v>0.01056475024690989</v>
+        <v>0.01060878578178825</v>
       </c>
       <c r="AE6">
-        <v>6698</v>
+        <v>6595</v>
       </c>
       <c r="AF6">
-        <v>0.200460898452698</v>
+        <v>0.2010486845715331</v>
       </c>
       <c r="AG6">
-        <v>8122</v>
+        <v>8001</v>
       </c>
       <c r="AH6">
-        <v>0.2430790410917906</v>
+        <v>0.2439106179312868</v>
       </c>
       <c r="AI6">
-        <v>47123</v>
+        <v>45976</v>
       </c>
       <c r="AJ6">
-        <v>28304</v>
+        <v>27575</v>
       </c>
       <c r="AK6">
-        <v>0.6006408760053477</v>
+        <v>0.5997694449277884</v>
       </c>
       <c r="AL6">
-        <v>2558</v>
+        <v>2496</v>
       </c>
       <c r="AM6">
-        <v>0.05428347091653758</v>
+        <v>0.05428919436227597</v>
       </c>
       <c r="AN6">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="AO6">
-        <v>0.009952677036691213</v>
+        <v>0.00989646772228989</v>
       </c>
       <c r="AP6">
-        <v>10099</v>
+        <v>9865</v>
       </c>
       <c r="AQ6">
-        <v>0.2143114827154468</v>
+        <v>0.2145684705063511</v>
       </c>
       <c r="AR6">
-        <v>5546</v>
+        <v>5434</v>
       </c>
       <c r="AS6">
-        <v>0.1176919975383571</v>
+        <v>0.118192100226205</v>
       </c>
       <c r="AT6">
-        <v>4524</v>
+        <v>4439</v>
       </c>
       <c r="AU6">
-        <v>1070</v>
+        <v>1051</v>
       </c>
       <c r="AV6">
-        <v>0.2365163572060124</v>
+        <v>0.2367650371705339</v>
       </c>
       <c r="AW6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AX6">
-        <v>0.01259946949602122</v>
+        <v>0.01239017796801081</v>
       </c>
       <c r="BA6">
-        <v>1429</v>
+        <v>1405</v>
       </c>
       <c r="BB6">
-        <v>0.3158709106984969</v>
+        <v>0.3165127280919126</v>
       </c>
       <c r="BC6">
-        <v>1968</v>
+        <v>1928</v>
       </c>
       <c r="BD6">
-        <v>0.4350132625994695</v>
+        <v>0.4343320567695427</v>
       </c>
       <c r="BE6">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="BF6">
         <v>125</v>
       </c>
       <c r="BG6">
-        <v>0.2115059221658206</v>
+        <v>0.2144082332761578</v>
       </c>
       <c r="BH6">
         <v>8</v>
       </c>
       <c r="BI6">
-        <v>0.01353637901861252</v>
+        <v>0.0137221269296741</v>
       </c>
       <c r="BL6">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BM6">
-        <v>0.3468697123519459</v>
+        <v>0.3481989708404803</v>
       </c>
       <c r="BN6">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="BO6">
-        <v>0.428087986463621</v>
+        <v>0.4236706689536878</v>
       </c>
       <c r="BP6">
-        <v>77199</v>
+        <v>74879</v>
       </c>
       <c r="BQ6">
-        <v>28025</v>
+        <v>27244</v>
       </c>
       <c r="BR6">
-        <v>0.3630228370833819</v>
+        <v>0.3638403290642236</v>
       </c>
       <c r="BS6">
-        <v>8547</v>
+        <v>8266</v>
       </c>
       <c r="BT6">
-        <v>0.1107138693506393</v>
+        <v>0.110391431509502</v>
       </c>
       <c r="BW6">
-        <v>21793</v>
+        <v>21105</v>
       </c>
       <c r="BX6">
-        <v>0.2822964028031451</v>
+        <v>0.2818547256240067</v>
       </c>
       <c r="BY6">
-        <v>18834</v>
+        <v>18264</v>
       </c>
       <c r="BZ6">
-        <v>0.2439668907628337</v>
+        <v>0.2439135138022677</v>
       </c>
       <c r="CA6">
-        <v>41043</v>
+        <v>40348</v>
       </c>
       <c r="CB6">
-        <v>17911</v>
+        <v>17622</v>
       </c>
       <c r="CC6">
-        <v>0.436395974953098</v>
+        <v>0.4367502726281352</v>
       </c>
       <c r="CD6">
-        <v>2231</v>
+        <v>2204</v>
       </c>
       <c r="CE6">
-        <v>0.05435762492995151</v>
+        <v>0.05462476454842867</v>
       </c>
       <c r="CF6">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="CG6">
-        <v>0.02648441878030358</v>
+        <v>0.02676712600376722</v>
       </c>
       <c r="CH6">
-        <v>9398</v>
+        <v>9234</v>
       </c>
       <c r="CI6">
-        <v>0.2289793631069854</v>
+        <v>0.2288589273322098</v>
       </c>
       <c r="CJ6">
-        <v>10416</v>
+        <v>10208</v>
       </c>
       <c r="CK6">
-        <v>0.2537826182296616</v>
+        <v>0.2529989094874591</v>
       </c>
     </row>
     <row r="7" spans="1:89">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -2325,58 +2299,58 @@
         <v>0.111001066585403</v>
       </c>
       <c r="AT7">
-        <v>4821</v>
+        <v>4628</v>
       </c>
       <c r="AU7">
-        <v>1167</v>
+        <v>1130</v>
       </c>
       <c r="AV7">
-        <v>0.2420659614187928</v>
+        <v>0.2441659464131374</v>
       </c>
       <c r="AW7">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="AX7">
-        <v>0.01369010578718108</v>
+        <v>0.01318063958513397</v>
       </c>
       <c r="BA7">
-        <v>1529</v>
+        <v>1476</v>
       </c>
       <c r="BB7">
-        <v>0.3171541174030284</v>
+        <v>0.3189282627484875</v>
       </c>
       <c r="BC7">
-        <v>2059</v>
+        <v>1961</v>
       </c>
       <c r="BD7">
-        <v>0.4270898153909977</v>
+        <v>0.4237251512532411</v>
       </c>
       <c r="BE7">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="BF7">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="BG7">
-        <v>0.3841463414634146</v>
+        <v>0.3734439834024896</v>
       </c>
       <c r="BH7">
         <v>1</v>
       </c>
       <c r="BI7">
-        <v>0.002032520325203252</v>
+        <v>0.002074688796680498</v>
       </c>
       <c r="BL7">
         <v>121</v>
       </c>
       <c r="BM7">
-        <v>0.2459349593495935</v>
+        <v>0.2510373443983402</v>
       </c>
       <c r="BN7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BO7">
-        <v>0.3678861788617886</v>
+        <v>0.3734439834024896</v>
       </c>
       <c r="BP7">
         <v>57549</v>
@@ -2450,84 +2424,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>57</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>67</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>68</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>78</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -2604,7 +2578,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -2644,13 +2618,13 @@
         <v>0.6378423153191596</v>
       </c>
       <c r="N3">
-        <v>3662</v>
+        <v>3708</v>
       </c>
       <c r="O3">
-        <v>926</v>
+        <v>939</v>
       </c>
       <c r="P3">
-        <v>0.2528672856362643</v>
+        <v>0.2532362459546926</v>
       </c>
       <c r="Q3">
         <v>844</v>
@@ -2662,26 +2636,26 @@
         <v>0.2298578199052133</v>
       </c>
       <c r="T3">
-        <v>45900</v>
+        <v>46209</v>
       </c>
       <c r="U3">
-        <v>16488</v>
+        <v>16594</v>
       </c>
       <c r="V3">
-        <v>0.3592156862745098</v>
+        <v>0.359107533164535</v>
       </c>
       <c r="W3">
-        <v>21030</v>
+        <v>21269</v>
       </c>
       <c r="X3">
-        <v>9399</v>
+        <v>9508</v>
       </c>
       <c r="Y3">
-        <v>0.4469329529243937</v>
+        <v>0.4470355917062391</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -2758,7 +2732,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -2835,84 +2809,84 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
-        <v>31919</v>
+        <v>31108</v>
       </c>
       <c r="C6">
-        <v>19354</v>
+        <v>18833</v>
       </c>
       <c r="D6">
-        <v>0.6063473166452583</v>
+        <v>0.6054069692683554</v>
       </c>
       <c r="E6">
-        <v>15204</v>
+        <v>14868</v>
       </c>
       <c r="F6">
-        <v>8950</v>
+        <v>8742</v>
       </c>
       <c r="G6">
-        <v>0.5886608787161274</v>
+        <v>0.5879741727199355</v>
       </c>
       <c r="H6">
-        <v>33413</v>
+        <v>32803</v>
       </c>
       <c r="I6">
-        <v>16486</v>
+        <v>16140</v>
       </c>
       <c r="J6">
-        <v>0.4934007721545506</v>
+        <v>0.4920281681553517</v>
       </c>
       <c r="K6">
-        <v>47123</v>
+        <v>45976</v>
       </c>
       <c r="L6">
-        <v>28304</v>
+        <v>27575</v>
       </c>
       <c r="M6">
-        <v>0.6006408760053477</v>
+        <v>0.5997694449277884</v>
       </c>
       <c r="N6">
-        <v>4524</v>
+        <v>4439</v>
       </c>
       <c r="O6">
-        <v>1070</v>
+        <v>1051</v>
       </c>
       <c r="P6">
-        <v>0.2365163572060124</v>
+        <v>0.2367650371705339</v>
       </c>
       <c r="Q6">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="R6">
         <v>125</v>
       </c>
       <c r="S6">
-        <v>0.2115059221658206</v>
+        <v>0.2144082332761578</v>
       </c>
       <c r="T6">
-        <v>77199</v>
+        <v>74879</v>
       </c>
       <c r="U6">
-        <v>28025</v>
+        <v>27244</v>
       </c>
       <c r="V6">
-        <v>0.3630228370833819</v>
+        <v>0.3638403290642236</v>
       </c>
       <c r="W6">
-        <v>41043</v>
+        <v>40348</v>
       </c>
       <c r="X6">
-        <v>17911</v>
+        <v>17622</v>
       </c>
       <c r="Y6">
-        <v>0.436395974953098</v>
+        <v>0.4367502726281352</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -2952,22 +2926,22 @@
         <v>0.625019046167911</v>
       </c>
       <c r="N7">
-        <v>4821</v>
+        <v>4628</v>
       </c>
       <c r="O7">
-        <v>1167</v>
+        <v>1130</v>
       </c>
       <c r="P7">
-        <v>0.2420659614187928</v>
+        <v>0.2441659464131374</v>
       </c>
       <c r="Q7">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="R7">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="S7">
-        <v>0.3841463414634146</v>
+        <v>0.3734439834024896</v>
       </c>
       <c r="T7">
         <v>57549</v>
@@ -2999,84 +2973,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>36</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>37</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>47</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>48</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>58</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>59</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>69</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>70</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>80</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -3153,7 +3127,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -3193,13 +3167,13 @@
         <v>0.04854539521574337</v>
       </c>
       <c r="N3">
-        <v>3662</v>
+        <v>3708</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P3">
-        <v>0.0204806116876024</v>
+        <v>0.02049622437971953</v>
       </c>
       <c r="Q3">
         <v>844</v>
@@ -3211,26 +3185,26 @@
         <v>0.01421800947867299</v>
       </c>
       <c r="T3">
-        <v>45900</v>
+        <v>46209</v>
       </c>
       <c r="U3">
-        <v>5350</v>
+        <v>5386</v>
       </c>
       <c r="V3">
-        <v>0.116557734204793</v>
+        <v>0.1165573805968534</v>
       </c>
       <c r="W3">
-        <v>21030</v>
+        <v>21269</v>
       </c>
       <c r="X3">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="Y3">
-        <v>0.06219686162624822</v>
+        <v>0.06159198833983733</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -3307,7 +3281,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -3384,84 +3358,84 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
-        <v>31919</v>
+        <v>31108</v>
       </c>
       <c r="C6">
-        <v>1638</v>
+        <v>1603</v>
       </c>
       <c r="D6">
-        <v>0.05131739716156521</v>
+        <v>0.05153015301530153</v>
       </c>
       <c r="E6">
-        <v>15204</v>
+        <v>14868</v>
       </c>
       <c r="F6">
-        <v>920</v>
+        <v>893</v>
       </c>
       <c r="G6">
-        <v>0.06051039200210471</v>
+        <v>0.06006187785848803</v>
       </c>
       <c r="H6">
-        <v>33413</v>
+        <v>32803</v>
       </c>
       <c r="I6">
-        <v>1732</v>
+        <v>1697</v>
       </c>
       <c r="J6">
-        <v>0.0518361116930536</v>
+        <v>0.05173307319452489</v>
       </c>
       <c r="K6">
-        <v>47123</v>
+        <v>45976</v>
       </c>
       <c r="L6">
-        <v>2558</v>
+        <v>2496</v>
       </c>
       <c r="M6">
-        <v>0.05428347091653758</v>
+        <v>0.05428919436227597</v>
       </c>
       <c r="N6">
-        <v>4524</v>
+        <v>4439</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>0.01259946949602122</v>
+        <v>0.01239017796801081</v>
       </c>
       <c r="Q6">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="R6">
         <v>8</v>
       </c>
       <c r="S6">
-        <v>0.01353637901861252</v>
+        <v>0.0137221269296741</v>
       </c>
       <c r="T6">
-        <v>77199</v>
+        <v>74879</v>
       </c>
       <c r="U6">
-        <v>8547</v>
+        <v>8266</v>
       </c>
       <c r="V6">
-        <v>0.1107138693506393</v>
+        <v>0.110391431509502</v>
       </c>
       <c r="W6">
-        <v>41043</v>
+        <v>40348</v>
       </c>
       <c r="X6">
-        <v>2231</v>
+        <v>2204</v>
       </c>
       <c r="Y6">
-        <v>0.05435762492995151</v>
+        <v>0.05462476454842867</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -3501,22 +3475,22 @@
         <v>0.0439331606480776</v>
       </c>
       <c r="N7">
-        <v>4821</v>
+        <v>4628</v>
       </c>
       <c r="O7">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="P7">
-        <v>0.01369010578718108</v>
+        <v>0.01318063958513397</v>
       </c>
       <c r="Q7">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="R7">
         <v>1</v>
       </c>
       <c r="S7">
-        <v>0.002032520325203252</v>
+        <v>0.002074688796680498</v>
       </c>
       <c r="T7">
         <v>57549</v>
@@ -3548,84 +3522,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>28</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>49</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>50</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>71</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>72</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -3684,7 +3658,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -3724,26 +3698,26 @@
         <v>0.007203996084239063</v>
       </c>
       <c r="N3">
-        <v>3662</v>
+        <v>3708</v>
       </c>
       <c r="Q3">
         <v>844</v>
       </c>
       <c r="T3">
-        <v>45900</v>
+        <v>46209</v>
       </c>
       <c r="W3">
-        <v>21030</v>
+        <v>21269</v>
       </c>
       <c r="X3">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Y3">
-        <v>0.01145981930575369</v>
+        <v>0.01166016267807607</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -3802,7 +3776,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -3861,66 +3835,66 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
-        <v>31919</v>
+        <v>31108</v>
       </c>
       <c r="C6">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="D6">
-        <v>0.009586766502709985</v>
+        <v>0.009483091166259483</v>
       </c>
       <c r="E6">
-        <v>15204</v>
+        <v>14868</v>
       </c>
       <c r="F6">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="G6">
-        <v>0.01072086293080768</v>
+        <v>0.01076136669357008</v>
       </c>
       <c r="H6">
-        <v>33413</v>
+        <v>32803</v>
       </c>
       <c r="I6">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J6">
-        <v>0.01056475024690989</v>
+        <v>0.01060878578178825</v>
       </c>
       <c r="K6">
-        <v>47123</v>
+        <v>45976</v>
       </c>
       <c r="L6">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="M6">
-        <v>0.009952677036691213</v>
+        <v>0.00989646772228989</v>
       </c>
       <c r="N6">
-        <v>4524</v>
+        <v>4439</v>
       </c>
       <c r="Q6">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="T6">
-        <v>77199</v>
+        <v>74879</v>
       </c>
       <c r="W6">
-        <v>41043</v>
+        <v>40348</v>
       </c>
       <c r="X6">
-        <v>1087</v>
+        <v>1080</v>
       </c>
       <c r="Y6">
-        <v>0.02648441878030358</v>
+        <v>0.02676712600376722</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -3960,10 +3934,10 @@
         <v>0.006069378840977195</v>
       </c>
       <c r="N7">
-        <v>4821</v>
+        <v>4628</v>
       </c>
       <c r="Q7">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="T7">
         <v>57549</v>
@@ -3989,84 +3963,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>51</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>52</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>62</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>63</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>73</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>74</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>84</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -4143,7 +4117,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -4183,13 +4157,13 @@
         <v>0.2020884058334798</v>
       </c>
       <c r="N3">
-        <v>3662</v>
+        <v>3708</v>
       </c>
       <c r="O3">
-        <v>1196</v>
+        <v>1211</v>
       </c>
       <c r="P3">
-        <v>0.326597487711633</v>
+        <v>0.3265911542610572</v>
       </c>
       <c r="Q3">
         <v>844</v>
@@ -4201,26 +4175,26 @@
         <v>0.3045023696682465</v>
       </c>
       <c r="T3">
-        <v>45900</v>
+        <v>46209</v>
       </c>
       <c r="U3">
-        <v>13096</v>
+        <v>13185</v>
       </c>
       <c r="V3">
-        <v>0.2853159041394335</v>
+        <v>0.2853340258391223</v>
       </c>
       <c r="W3">
-        <v>21030</v>
+        <v>21269</v>
       </c>
       <c r="X3">
-        <v>4772</v>
+        <v>4825</v>
       </c>
       <c r="Y3">
-        <v>0.2269139324774132</v>
+        <v>0.2268559875875688</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -4297,7 +4271,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -4374,84 +4348,84 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
-        <v>31919</v>
+        <v>31108</v>
       </c>
       <c r="C6">
-        <v>7172</v>
+        <v>6993</v>
       </c>
       <c r="D6">
-        <v>0.2246937560700523</v>
+        <v>0.2247974797479748</v>
       </c>
       <c r="E6">
-        <v>15204</v>
+        <v>14868</v>
       </c>
       <c r="F6">
-        <v>2927</v>
+        <v>2872</v>
       </c>
       <c r="G6">
-        <v>0.1925151275980005</v>
+        <v>0.193166532149583</v>
       </c>
       <c r="H6">
-        <v>33413</v>
+        <v>32803</v>
       </c>
       <c r="I6">
-        <v>6698</v>
+        <v>6595</v>
       </c>
       <c r="J6">
-        <v>0.200460898452698</v>
+        <v>0.2010486845715331</v>
       </c>
       <c r="K6">
-        <v>47123</v>
+        <v>45976</v>
       </c>
       <c r="L6">
-        <v>10099</v>
+        <v>9865</v>
       </c>
       <c r="M6">
-        <v>0.2143114827154468</v>
+        <v>0.2145684705063511</v>
       </c>
       <c r="N6">
-        <v>4524</v>
+        <v>4439</v>
       </c>
       <c r="O6">
-        <v>1429</v>
+        <v>1405</v>
       </c>
       <c r="P6">
-        <v>0.3158709106984969</v>
+        <v>0.3165127280919126</v>
       </c>
       <c r="Q6">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="R6">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="S6">
-        <v>0.3468697123519459</v>
+        <v>0.3481989708404803</v>
       </c>
       <c r="T6">
-        <v>77199</v>
+        <v>74879</v>
       </c>
       <c r="U6">
-        <v>21793</v>
+        <v>21105</v>
       </c>
       <c r="V6">
-        <v>0.2822964028031451</v>
+        <v>0.2818547256240067</v>
       </c>
       <c r="W6">
-        <v>41043</v>
+        <v>40348</v>
       </c>
       <c r="X6">
-        <v>9398</v>
+        <v>9234</v>
       </c>
       <c r="Y6">
-        <v>0.2289793631069854</v>
+        <v>0.2288589273322098</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -4491,22 +4465,22 @@
         <v>0.2124536543247499</v>
       </c>
       <c r="N7">
-        <v>4821</v>
+        <v>4628</v>
       </c>
       <c r="O7">
-        <v>1529</v>
+        <v>1476</v>
       </c>
       <c r="P7">
-        <v>0.3171541174030284</v>
+        <v>0.3189282627484875</v>
       </c>
       <c r="Q7">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="R7">
         <v>121</v>
       </c>
       <c r="S7">
-        <v>0.2459349593495935</v>
+        <v>0.2510373443983402</v>
       </c>
       <c r="T7">
         <v>57549</v>
@@ -4538,84 +4512,84 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>43</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>53</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>54</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>55</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>65</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>66</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" t="s">
         <v>76</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" t="s">
         <v>86</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
       <c r="B2">
@@ -4692,7 +4666,7 @@
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
       <c r="B3">
@@ -4732,13 +4706,13 @@
         <v>0.1035166545345014</v>
       </c>
       <c r="N3">
-        <v>3662</v>
+        <v>3708</v>
       </c>
       <c r="O3">
-        <v>1465</v>
+        <v>1482</v>
       </c>
       <c r="P3">
-        <v>0.4000546149645003</v>
+        <v>0.3996763754045308</v>
       </c>
       <c r="Q3">
         <v>844</v>
@@ -4750,26 +4724,26 @@
         <v>0.4514218009478673</v>
       </c>
       <c r="T3">
-        <v>45900</v>
+        <v>46209</v>
       </c>
       <c r="U3">
-        <v>10966</v>
+        <v>11044</v>
       </c>
       <c r="V3">
-        <v>0.2389106753812636</v>
+        <v>0.2390010603994893</v>
       </c>
       <c r="W3">
-        <v>21030</v>
+        <v>21269</v>
       </c>
       <c r="X3">
-        <v>5310</v>
+        <v>5378</v>
       </c>
       <c r="Y3">
-        <v>0.2524964336661912</v>
+        <v>0.2528562696882787</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>91</v>
       </c>
       <c r="B4">
@@ -4846,7 +4820,7 @@
       </c>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>92</v>
       </c>
       <c r="B5">
@@ -4923,84 +4897,84 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>93</v>
       </c>
       <c r="B6">
-        <v>31919</v>
+        <v>31108</v>
       </c>
       <c r="C6">
-        <v>3317</v>
+        <v>3248</v>
       </c>
       <c r="D6">
-        <v>0.1039192957172844</v>
+        <v>0.1044104410441044</v>
       </c>
       <c r="E6">
-        <v>15204</v>
+        <v>14868</v>
       </c>
       <c r="F6">
-        <v>2229</v>
+        <v>2186</v>
       </c>
       <c r="G6">
-        <v>0.1466061562746646</v>
+        <v>0.1470271724509013</v>
       </c>
       <c r="H6">
-        <v>33413</v>
+        <v>32803</v>
       </c>
       <c r="I6">
-        <v>8122</v>
+        <v>8001</v>
       </c>
       <c r="J6">
-        <v>0.2430790410917906</v>
+        <v>0.2439106179312868</v>
       </c>
       <c r="K6">
-        <v>47123</v>
+        <v>45976</v>
       </c>
       <c r="L6">
-        <v>5546</v>
+        <v>5434</v>
       </c>
       <c r="M6">
-        <v>0.1176919975383571</v>
+        <v>0.118192100226205</v>
       </c>
       <c r="N6">
-        <v>4524</v>
+        <v>4439</v>
       </c>
       <c r="O6">
-        <v>1968</v>
+        <v>1928</v>
       </c>
       <c r="P6">
-        <v>0.4350132625994695</v>
+        <v>0.4343320567695427</v>
       </c>
       <c r="Q6">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="R6">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="S6">
-        <v>0.428087986463621</v>
+        <v>0.4236706689536878</v>
       </c>
       <c r="T6">
-        <v>77199</v>
+        <v>74879</v>
       </c>
       <c r="U6">
-        <v>18834</v>
+        <v>18264</v>
       </c>
       <c r="V6">
-        <v>0.2439668907628337</v>
+        <v>0.2439135138022677</v>
       </c>
       <c r="W6">
-        <v>41043</v>
+        <v>40348</v>
       </c>
       <c r="X6">
-        <v>10416</v>
+        <v>10208</v>
       </c>
       <c r="Y6">
-        <v>0.2537826182296616</v>
+        <v>0.2529989094874591</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -5040,22 +5014,22 @@
         <v>0.111001066585403</v>
       </c>
       <c r="N7">
-        <v>4821</v>
+        <v>4628</v>
       </c>
       <c r="O7">
-        <v>2059</v>
+        <v>1961</v>
       </c>
       <c r="P7">
-        <v>0.4270898153909977</v>
+        <v>0.4237251512532411</v>
       </c>
       <c r="Q7">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="R7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="S7">
-        <v>0.3678861788617886</v>
+        <v>0.3734439834024896</v>
       </c>
       <c r="T7">
         <v>57549</v>
